--- a/artfynd/A 22408-2023 artfynd.xlsx
+++ b/artfynd/A 22408-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22408-2023 artfynd.xlsx
+++ b/artfynd/A 22408-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,37 +1033,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96071235</v>
+        <v>96071237</v>
       </c>
       <c r="B5" t="n">
-        <v>90671</v>
+        <v>91626</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1076,16 +1076,18 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lillla Lobråten, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508335.7311242975</v>
+        <v>508335</v>
       </c>
       <c r="R5" t="n">
-        <v>6601034.604142958</v>
+        <v>6601032</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,19 +1117,9 @@
           <t>2021-09-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,6 +1128,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,125 +1149,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>96071237</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91626</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sarcodon imbricatus s.str.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Lillla Lobråten, Vstm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>508335</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6601032</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Örebro</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2021-09-13</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Emil Pagstedt Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
